--- a/examples/merged-transactions.xlsx
+++ b/examples/merged-transactions.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3Rivers FCU</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3Rivers FCU</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3Rivers FCU</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3Rivers FCU</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3Rivers FCU</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3Rivers FCU</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3Rivers FCU</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Discover Bank</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Discover Bank</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Discover Bank</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Discover Bank</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Discover Bank</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Discover Card</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Discover Card</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Discover Card</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Discover Card</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Discover Card</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
